--- a/output/topology_excel/11814.xlsx
+++ b/output/topology_excel/11814.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="F2" t="n">
         <v>14</v>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -498,18 +498,18 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -523,15 +523,15 @@
         <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,18 +542,18 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,18 +564,18 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,18 +586,18 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -619,7 +619,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,18 +630,18 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -649,21 +649,21 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -677,37 +677,37 @@
         <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>62</v>
+      </c>
+      <c r="F12" t="n">
         <v>11</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Door</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>91</v>
-      </c>
-      <c r="F12" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,54 +806,54 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>393</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>332</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>146</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="F20" t="n">
-        <v>127</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>332</v>
+        <v>116</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>337</v>
+        <v>119</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="F24" t="n">
         <v>14</v>
@@ -968,11 +968,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="B25" t="n">
-        <v>6</v>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>460</v>
+        <v>332</v>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,19 +1004,19 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>398</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
         <v>6</v>
       </c>
-      <c r="B27" t="n">
-        <v>7</v>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>394</v>
+        <v>337</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F28" t="n">
-        <v>230</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>186</v>
+        <v>460</v>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>183</v>
+        <v>398</v>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,15 +1180,15 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="F34" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B35" t="n">
         <v>18</v>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="F36" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B37" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="F37" t="n">
-        <v>53</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B39" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>286</v>
+        <v>340</v>
       </c>
       <c r="F39" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,32 +1312,340 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>289</v>
+        <v>105</v>
       </c>
       <c r="F40" t="n">
-        <v>146</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>318</v>
+      </c>
+      <c r="F41" t="n">
         <v>17</v>
       </c>
-      <c r="B41" t="n">
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" t="n">
         <v>18</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>340</v>
-      </c>
-      <c r="F41" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>314</v>
+      </c>
+      <c r="F42" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>11</v>
+      </c>
+      <c r="B43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>375</v>
+      </c>
+      <c r="F43" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>270</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>106</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B47" t="n">
+        <v>14</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>286</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>16</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>376</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>17</v>
+      </c>
+      <c r="B49" t="n">
+        <v>19</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>335</v>
+      </c>
+      <c r="F49" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>18</v>
+      </c>
+      <c r="B50" t="n">
+        <v>20</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>183</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>73</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>77</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>371</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>119</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/11814.xlsx
+++ b/output/topology_excel/11814.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
         </is>
       </c>
     </row>
@@ -481,6 +521,14 @@
       <c r="F2" t="n">
         <v>14</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +551,14 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +581,14 @@
       <c r="F4" t="n">
         <v>22</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +611,14 @@
       <c r="F5" t="n">
         <v>15</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +641,14 @@
       <c r="F6" t="n">
         <v>17</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +671,14 @@
       <c r="F7" t="n">
         <v>17</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +701,14 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +731,14 @@
       <c r="F9" t="n">
         <v>22</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -649,7 +753,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>172</v>
@@ -657,6 +761,14 @@
       <c r="F10" t="n">
         <v>22</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +791,14 @@
       <c r="F11" t="n">
         <v>14</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +821,14 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +851,14 @@
       <c r="F13" t="n">
         <v>22</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +881,14 @@
       <c r="F14" t="n">
         <v>20</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +911,14 @@
       <c r="F15" t="n">
         <v>19</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +941,14 @@
       <c r="F16" t="n">
         <v>21</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +971,14 @@
       <c r="F17" t="n">
         <v>21</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +1001,14 @@
       <c r="F18" t="n">
         <v>18</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +1031,14 @@
       <c r="F19" t="n">
         <v>18</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -869,14 +1053,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>450</v>
+        <v>235</v>
       </c>
       <c r="F20" t="n">
-        <v>235</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>27</v>
+      </c>
+      <c r="H20" t="n">
+        <v>22</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1095,14 @@
       <c r="F21" t="n">
         <v>72</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -913,14 +1117,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>233</v>
+        <v>91</v>
       </c>
       <c r="F22" t="n">
         <v>15</v>
       </c>
+      <c r="G22" t="n">
+        <v>23</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1159,14 @@
       <c r="F23" t="n">
         <v>15</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1189,14 @@
       <c r="F24" t="n">
         <v>14</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -979,13 +1211,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="F25" t="n">
+        <v>22</v>
+      </c>
+      <c r="G25" t="n">
+        <v>26</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>32</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>37</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
         <v>41</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1009,6 +1265,14 @@
       <c r="F26" t="n">
         <v>22</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1295,14 @@
       <c r="F27" t="n">
         <v>19</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1325,14 @@
       <c r="F28" t="n">
         <v>14</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1073,8 +1353,16 @@
         <v>460</v>
       </c>
       <c r="F29" t="n">
-        <v>135</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1095,8 +1383,16 @@
         <v>398</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1415,14 @@
       <c r="F31" t="n">
         <v>22</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1133,14 +1437,26 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F32" t="n">
-        <v>138</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G32" t="n">
+        <v>118</v>
+      </c>
+      <c r="H32" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1479,14 @@
       <c r="F33" t="n">
         <v>20</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1509,14 @@
       <c r="F34" t="n">
         <v>11</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1539,14 @@
       <c r="F35" t="n">
         <v>11</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1569,14 @@
       <c r="F36" t="n">
         <v>44</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1243,14 +1591,26 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>289</v>
+        <v>128</v>
       </c>
       <c r="F37" t="n">
-        <v>146</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G37" t="n">
+        <v>270</v>
+      </c>
+      <c r="H37" t="n">
+        <v>18</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1633,14 @@
       <c r="F38" t="n">
         <v>53</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1663,14 @@
       <c r="F39" t="n">
         <v>18</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1693,14 @@
       <c r="F40" t="n">
         <v>17</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1723,14 @@
       <c r="F41" t="n">
         <v>17</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1353,14 +1745,30 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="F42" t="n">
-        <v>146</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G42" t="n">
+        <v>124</v>
+      </c>
+      <c r="H42" t="n">
+        <v>11</v>
+      </c>
+      <c r="I42" t="n">
+        <v>184</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1791,14 @@
       <c r="F43" t="n">
         <v>19</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1821,14 @@
       <c r="F44" t="n">
         <v>21</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1851,14 @@
       <c r="F45" t="n">
         <v>31</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1881,14 @@
       <c r="F46" t="n">
         <v>21</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1911,14 @@
       <c r="F47" t="n">
         <v>21</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1941,14 @@
       <c r="F48" t="n">
         <v>14</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1507,14 +1963,30 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="F49" t="n">
-        <v>230</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G49" t="n">
+        <v>216</v>
+      </c>
+      <c r="H49" t="n">
+        <v>18</v>
+      </c>
+      <c r="I49" t="n">
+        <v>216</v>
+      </c>
+      <c r="J49" t="n">
+        <v>14</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +2009,14 @@
       <c r="F50" t="n">
         <v>22</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +2039,14 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1573,7 +2061,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>77</v>
@@ -1581,13 +2069,25 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
+      <c r="G52" t="n">
+        <v>371</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>1</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +2098,26 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>371</v>
+        <v>5</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>1</v>
       </c>
       <c r="B54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,33 +2128,19 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" t="n">
-        <v>10</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>119</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
